--- a/SSIS-Project/Timesheets/Jabulane/Jabulane_Poulo_April_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Jabulane/Jabulane_Poulo_April_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jabulane Poulo\Downloads\Timesheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{719D81F0-BC2F-488B-A237-0367FBC5CE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{719D81F0-BC2F-488B-A237-0367FBC5CE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7719EBE-FAEB-4D50-830D-EFECA04A967C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="260">
   <si>
     <t>Consultant</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>Meeting with Bongani Mondlane and the team to discussed the Udemy  GitHub Actions course</t>
-  </si>
-  <si>
-    <t>Thugthrsday</t>
   </si>
   <si>
     <t xml:space="preserve">One on one meeting with Bongani Mondlane </t>
@@ -1932,28 +1929,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1969,6 +1951,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6408,7 +6405,7 @@
         <v>46135</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="C101" s="27" t="s">
         <v>14</v>
@@ -6421,7 +6418,7 @@
         <v>16</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H101" s="29">
         <f t="shared" si="1"/>
@@ -6514,7 +6511,7 @@
         <v>16</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H104" s="29">
         <f t="shared" si="1"/>
@@ -6607,7 +6604,7 @@
         <v>16</v>
       </c>
       <c r="G107" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H107" s="29">
         <f t="shared" si="1"/>
@@ -6638,7 +6635,7 @@
         <v>16</v>
       </c>
       <c r="G108" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H108" s="29">
         <f t="shared" si="1"/>
@@ -6669,7 +6666,7 @@
         <v>16</v>
       </c>
       <c r="G109" s="28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H109" s="29">
         <f t="shared" si="1"/>
@@ -6738,7 +6735,7 @@
         <v>16</v>
       </c>
       <c r="G112" s="49" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H112" s="50">
         <f t="shared" si="1"/>
@@ -6800,7 +6797,7 @@
         <v>16</v>
       </c>
       <c r="G114" s="28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H114" s="29">
         <f t="shared" si="1"/>
@@ -6862,7 +6859,7 @@
         <v>16</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H116" s="29">
         <f t="shared" si="1"/>
@@ -6893,7 +6890,7 @@
         <v>16</v>
       </c>
       <c r="G117" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H117" s="29">
         <f t="shared" si="1"/>
@@ -6986,7 +6983,7 @@
         <v>16</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H120" s="29">
         <f t="shared" si="1"/>
@@ -7017,7 +7014,7 @@
         <v>16</v>
       </c>
       <c r="G121" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H121" s="29">
         <f t="shared" si="1"/>
@@ -7079,7 +7076,7 @@
         <v>16</v>
       </c>
       <c r="G123" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H123" s="29">
         <f t="shared" si="1"/>
@@ -7110,7 +7107,7 @@
         <v>16</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H124" s="29">
         <f t="shared" si="1"/>
@@ -7141,7 +7138,7 @@
         <v>16</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H125" s="29">
         <f t="shared" si="1"/>
@@ -7203,7 +7200,7 @@
         <v>16</v>
       </c>
       <c r="G127" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H127" s="29">
         <f t="shared" si="1"/>
@@ -7234,7 +7231,7 @@
         <v>16</v>
       </c>
       <c r="G128" s="28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H128" s="29">
         <f t="shared" si="1"/>
@@ -7265,7 +7262,7 @@
         <v>16</v>
       </c>
       <c r="G129" s="28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H129" s="29">
         <f t="shared" si="1"/>
@@ -7296,7 +7293,7 @@
         <v>16</v>
       </c>
       <c r="G130" s="28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H130" s="29">
         <f t="shared" si="1"/>
@@ -7327,7 +7324,7 @@
         <v>16</v>
       </c>
       <c r="G131" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H131" s="29">
         <f t="shared" si="1"/>
@@ -7358,7 +7355,7 @@
         <v>16</v>
       </c>
       <c r="G132" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H132" s="29">
         <f t="shared" si="1"/>
@@ -7385,7 +7382,7 @@
       <c r="C134" s="5"/>
       <c r="D134" s="6"/>
       <c r="E134" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F134" s="8">
         <v>152</v>
@@ -7398,7 +7395,7 @@
       <c r="C135" s="9"/>
       <c r="D135" s="2"/>
       <c r="E135" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F135" s="11">
         <v>19</v>
@@ -7407,7 +7404,7 @@
     </row>
     <row r="136" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A136" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B136" s="125"/>
       <c r="C136" s="125"/>
@@ -7422,7 +7419,7 @@
       <c r="C137" s="6"/>
       <c r="D137" s="6"/>
       <c r="E137" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F137" s="15">
         <f>SUMIF(F9:F132,"Billable",H9:H132)</f>
@@ -7432,13 +7429,13 @@
     </row>
     <row r="138" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A138" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B138" s="126"/>
       <c r="C138" s="126"/>
       <c r="D138" s="16"/>
       <c r="E138" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F138" s="18">
         <f>SUMIF(F9:F132,"Non-Billable",H9:H132)</f>
@@ -7452,7 +7449,7 @@
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F139" s="44">
         <f>F137+F138</f>
@@ -7475,7 +7472,7 @@
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F141" s="21"/>
       <c r="H141" s="40"/>
@@ -7605,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -7677,7 +7674,7 @@
         <v>16</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H9" s="50">
         <f t="shared" ref="H9:H39" si="0">J9-I9</f>
@@ -7739,16 +7736,16 @@
         <v>14</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="G12" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
@@ -8291,7 +8288,7 @@
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="8">
         <v>160</v>
@@ -8304,7 +8301,7 @@
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="11">
         <v>20</v>
@@ -8313,7 +8310,7 @@
     </row>
     <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" s="125"/>
       <c r="C43" s="125"/>
@@ -8328,7 +8325,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -8338,13 +8335,13 @@
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B45" s="126"/>
       <c r="C45" s="126"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -8358,7 +8355,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -8381,7 +8378,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
@@ -8514,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -8579,16 +8576,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="H9" s="29">
         <f t="shared" ref="H9" si="0">J9-I9</f>
@@ -8885,7 +8882,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="50">
         <f t="shared" si="1"/>
@@ -9181,7 +9178,7 @@
       <c r="C40" s="5"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="8">
         <v>168</v>
@@ -9194,7 +9191,7 @@
       <c r="C41" s="9"/>
       <c r="D41" s="2"/>
       <c r="E41" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="11">
         <v>21</v>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" s="125"/>
       <c r="C42" s="125"/>
@@ -9218,7 +9215,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F43" s="15">
         <f>SUMIF(F9:F38,"Billable",H9:H38)</f>
@@ -9228,13 +9225,13 @@
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A44" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B44" s="126"/>
       <c r="C44" s="126"/>
       <c r="D44" s="16"/>
       <c r="E44" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44" s="18">
         <f>SUMIF(F9:F38,"Non-Billable",H9:H38)</f>
@@ -9248,7 +9245,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F45" s="44">
         <f>F43+F44</f>
@@ -9271,7 +9268,7 @@
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
@@ -9410,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -9475,16 +9472,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="H9" s="29">
         <f>J9-I9</f>
@@ -10084,7 +10081,7 @@
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="8">
         <v>184</v>
@@ -10097,7 +10094,7 @@
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="11">
         <v>23</v>
@@ -10106,7 +10103,7 @@
     </row>
     <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" s="125"/>
       <c r="C43" s="125"/>
@@ -10121,7 +10118,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -10131,13 +10128,13 @@
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B45" s="126"/>
       <c r="C45" s="126"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -10151,7 +10148,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -10174,7 +10171,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
@@ -10317,7 +10314,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -10420,16 +10417,16 @@
         <v>14</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="G11" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="G11" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="H11" s="29">
         <f t="shared" ref="H11" si="1">J11-I11</f>
@@ -10549,7 +10546,7 @@
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H17" s="34">
         <f t="shared" si="2"/>
@@ -10576,7 +10573,7 @@
         <v>16</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H18" s="50">
         <f t="shared" si="2"/>
@@ -11005,7 +11002,7 @@
       <c r="C41" s="5"/>
       <c r="D41" s="6"/>
       <c r="E41" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" s="8">
         <v>160</v>
@@ -11018,7 +11015,7 @@
       <c r="C42" s="9"/>
       <c r="D42" s="2"/>
       <c r="E42" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="11">
         <v>20</v>
@@ -11027,7 +11024,7 @@
     </row>
     <row r="43" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A43" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" s="125"/>
       <c r="C43" s="125"/>
@@ -11042,7 +11039,7 @@
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F44" s="15">
         <f>SUMIF(F9:F39,"Billable",H9:H39)</f>
@@ -11052,13 +11049,13 @@
     </row>
     <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A45" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B45" s="126"/>
       <c r="C45" s="126"/>
       <c r="D45" s="16"/>
       <c r="E45" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F45" s="18">
         <f>SUMIF(F9:F39,"Non-Billable",H9:H39)</f>
@@ -11072,7 +11069,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F46" s="44">
         <f>F44+F45</f>
@@ -11095,7 +11092,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
@@ -11228,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -11293,16 +11290,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="G9" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="G9" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="H9" s="29">
         <f t="shared" ref="H9" si="0">J9-I9</f>
@@ -11751,7 +11748,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" s="50">
         <f t="shared" ref="H32" si="2">J32-I32</f>
@@ -11895,7 +11892,7 @@
       <c r="C40" s="5"/>
       <c r="D40" s="6"/>
       <c r="E40" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F40" s="8">
         <v>168</v>
@@ -11908,7 +11905,7 @@
       <c r="C41" s="9"/>
       <c r="D41" s="2"/>
       <c r="E41" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="11">
         <v>21</v>
@@ -11917,7 +11914,7 @@
     </row>
     <row r="42" spans="1:10" ht="13.9" customHeight="1" thickBot="1">
       <c r="A42" s="125" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" s="125"/>
       <c r="C42" s="125"/>
@@ -11932,7 +11929,7 @@
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F43" s="15">
         <f>SUMIF(F9:F38,"Billable",H9:H38)</f>
@@ -11942,13 +11939,13 @@
     </row>
     <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1">
       <c r="A44" s="126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B44" s="126"/>
       <c r="C44" s="126"/>
       <c r="D44" s="16"/>
       <c r="E44" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44" s="18">
         <f>SUMIF(F9:F38,"Non-Billable",H9:H38)</f>
@@ -11962,7 +11959,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F45" s="44">
         <f>F43+F44</f>
@@ -11985,7 +11982,7 @@
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
@@ -12166,7 +12163,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="86"/>
       <c r="D5" s="86"/>
@@ -12175,7 +12172,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="81">
         <f>F17</f>
@@ -12195,132 +12192,132 @@
       <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:15" ht="27.4" customHeight="1">
-      <c r="A8" s="132" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
+      <c r="A8" s="135" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1">
       <c r="A9" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="138" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="C9" s="139"/>
+      <c r="D9" s="138" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="129" t="s">
+      <c r="E9" s="139"/>
+      <c r="F9" s="83" t="s">
         <v>90</v>
-      </c>
-      <c r="E9" s="130"/>
-      <c r="F9" s="83" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="78">
         <v>46113</v>
       </c>
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="129" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="131"/>
+      <c r="E10" s="129"/>
       <c r="F10" s="77">
         <v>200</v>
       </c>
-      <c r="G10" s="127" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
+      <c r="G10" s="136" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
+      <c r="L10" s="137"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="137"/>
+      <c r="O10" s="137"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="78">
         <v>46113</v>
       </c>
-      <c r="B11" s="133" t="s">
+      <c r="B11" s="127" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="128"/>
+      <c r="D11" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="131" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="131"/>
+      <c r="E11" s="129"/>
       <c r="F11" s="77"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="78">
         <v>46113</v>
       </c>
-      <c r="B12" s="133" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
+      <c r="B12" s="127" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="128"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="77"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="78">
         <v>46113</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
+      <c r="B13" s="127"/>
+      <c r="C13" s="128"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
       <c r="F13" s="77"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="78">
         <v>46113</v>
       </c>
-      <c r="B14" s="133"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
       <c r="F14" s="77"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="78">
         <v>46113</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="77"/>
     </row>
     <row r="16" spans="1:15" ht="13.15" thickBot="1">
       <c r="A16" s="78">
         <v>46113</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="129"/>
+      <c r="E16" s="129"/>
       <c r="F16" s="77"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A17" s="135" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="136"/>
-      <c r="E17" s="137"/>
+      <c r="A17" s="130" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="132"/>
       <c r="F17" s="76">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -12336,6 +12333,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -12345,16 +12352,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -12406,13 +12403,13 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B6" s="123"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="124"/>
     </row>
@@ -12422,7 +12419,7 @@
     </row>
     <row r="9" spans="1:6" ht="27.4" customHeight="1">
       <c r="A9" s="153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="153"/>
       <c r="C9" s="153"/>
@@ -12432,27 +12429,27 @@
     </row>
     <row r="10" spans="1:6" ht="25.15">
       <c r="A10" s="87" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="C10" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="D10" s="87" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="87" t="s">
+      <c r="E10" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="87" t="s">
+      <c r="F10" s="87" t="s">
         <v>106</v>
-      </c>
-      <c r="F10" s="87" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="117">
         <v>46161</v>
@@ -12465,7 +12462,7 @@
       </c>
       <c r="E11" s="87"/>
       <c r="F11" s="87" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -12505,7 +12502,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="154" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B16" s="155"/>
       <c r="C16" s="155"/>
@@ -12550,7 +12547,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="149"/>
       <c r="C22" s="149"/>
@@ -12560,7 +12557,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.15" thickBot="1">
       <c r="A23" s="94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B23" s="151"/>
       <c r="C23" s="151"/>
@@ -12638,30 +12635,30 @@
         <v>14</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F2" s="52" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J2" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="71" t="s">
+      <c r="F3" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="68" t="s">
         <v>116</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="68" t="s">
-        <v>117</v>
       </c>
       <c r="I3" s="99"/>
       <c r="J3" s="56" t="s">
@@ -12670,337 +12667,337 @@
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="54" t="s">
         <v>118</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>119</v>
       </c>
       <c r="F4" s="57" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" s="68"/>
       <c r="J4" s="58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="F5" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="H5" s="68" t="s">
         <v>123</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>124</v>
       </c>
       <c r="I5" s="100"/>
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="66" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="F6" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="H6" s="99" t="s">
         <v>127</v>
-      </c>
-      <c r="H6" s="99" t="s">
-        <v>128</v>
       </c>
       <c r="I6" s="101"/>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="66" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="F7" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="H7" s="67" t="s">
         <v>131</v>
-      </c>
-      <c r="H7" s="67" t="s">
-        <v>132</v>
       </c>
       <c r="I7" s="102"/>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="F8" s="57" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="H8" s="102" t="s">
         <v>135</v>
-      </c>
-      <c r="H8" s="102" t="s">
-        <v>136</v>
       </c>
       <c r="I8" s="99"/>
       <c r="J8" s="52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="F9" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="H9" s="103" t="s">
         <v>140</v>
-      </c>
-      <c r="H9" s="103" t="s">
-        <v>141</v>
       </c>
       <c r="I9" s="99"/>
       <c r="J9" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="F10" s="57" t="s">
         <v>143</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="H10" s="107" t="s">
         <v>144</v>
-      </c>
-      <c r="H10" s="107" t="s">
-        <v>145</v>
       </c>
       <c r="I10" s="102"/>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="F11" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="H11" s="103" t="s">
         <v>148</v>
-      </c>
-      <c r="H11" s="103" t="s">
-        <v>149</v>
       </c>
       <c r="I11" s="102"/>
       <c r="J11" s="52" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="57" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="H12" s="107" t="s">
         <v>152</v>
-      </c>
-      <c r="H12" s="107" t="s">
-        <v>153</v>
       </c>
       <c r="I12" s="103"/>
       <c r="J12" s="52" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="F13" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="H13" s="104" t="s">
         <v>156</v>
-      </c>
-      <c r="H13" s="104" t="s">
-        <v>157</v>
       </c>
       <c r="I13" s="103"/>
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" s="60"/>
       <c r="F14" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="105" t="s">
         <v>159</v>
-      </c>
-      <c r="H14" s="105" t="s">
-        <v>160</v>
       </c>
       <c r="I14" s="104"/>
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="66" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D15" s="61"/>
       <c r="F15" s="59" t="s">
         <v>38</v>
       </c>
       <c r="H15" s="103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I15" s="103"/>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="66" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D16" s="61"/>
       <c r="F16" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="104" t="s">
         <v>164</v>
-      </c>
-      <c r="H16" s="104" t="s">
-        <v>165</v>
       </c>
       <c r="I16" s="105"/>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="66" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="61"/>
       <c r="F17" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="67" t="s">
         <v>167</v>
-      </c>
-      <c r="H17" s="67" t="s">
-        <v>168</v>
       </c>
       <c r="I17" s="103"/>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D18" s="61"/>
       <c r="F18" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="H18" s="108" t="s">
         <v>170</v>
-      </c>
-      <c r="H18" s="108" t="s">
-        <v>171</v>
       </c>
       <c r="I18" s="105"/>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D19" s="61"/>
       <c r="F19" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" s="106"/>
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D20" s="61"/>
       <c r="F20" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="70" t="s">
         <v>175</v>
-      </c>
-      <c r="H20" s="70" t="s">
-        <v>176</v>
       </c>
       <c r="I20" s="104"/>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="66" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D21" s="61"/>
       <c r="F21" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="112" t="s">
         <v>178</v>
-      </c>
-      <c r="H21" s="112" t="s">
-        <v>179</v>
       </c>
       <c r="I21" s="102"/>
     </row>
     <row r="22" spans="2:9" ht="27.6">
       <c r="B22" s="66" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D22" s="61"/>
       <c r="F22" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="118" t="s">
         <v>181</v>
-      </c>
-      <c r="H22" s="118" t="s">
-        <v>182</v>
       </c>
       <c r="I22" s="107"/>
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D23" s="61"/>
       <c r="F23" s="59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H23" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I23" s="108"/>
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D24" s="61"/>
       <c r="F24" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="70" t="s">
         <v>186</v>
-      </c>
-      <c r="H24" s="70" t="s">
-        <v>187</v>
       </c>
       <c r="I24" s="109"/>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="66" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="61"/>
       <c r="F25" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="112" t="s">
         <v>189</v>
-      </c>
-      <c r="H25" s="112" t="s">
-        <v>190</v>
       </c>
       <c r="I25" s="110"/>
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="66" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="F26" s="57" t="s">
+      <c r="H26" s="70" t="s">
         <v>192</v>
-      </c>
-      <c r="H26" s="70" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="66" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" s="61"/>
       <c r="F27" s="59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H27" s="109" t="s">
         <v>1</v>
@@ -13009,312 +13006,312 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" s="61"/>
       <c r="F28" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="H28" s="112" t="s">
         <v>197</v>
-      </c>
-      <c r="H28" s="112" t="s">
-        <v>198</v>
       </c>
       <c r="I28" s="70"/>
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="66" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="F29" s="59" t="s">
+      <c r="H29" s="110" t="s">
         <v>200</v>
-      </c>
-      <c r="H29" s="110" t="s">
-        <v>201</v>
       </c>
       <c r="I29" s="111"/>
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="66" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="F30" s="57" t="s">
+      <c r="H30" s="69" t="s">
         <v>203</v>
-      </c>
-      <c r="H30" s="69" t="s">
-        <v>204</v>
       </c>
       <c r="I30" s="109"/>
     </row>
     <row r="31" spans="2:9">
       <c r="B31" s="66" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="F31" s="59" t="s">
+      <c r="H31" s="69" t="s">
         <v>206</v>
-      </c>
-      <c r="H31" s="69" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="66" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="F32" s="57" t="s">
+      <c r="H32" s="111" t="s">
         <v>209</v>
-      </c>
-      <c r="H32" s="111" t="s">
-        <v>210</v>
       </c>
       <c r="I32" s="110"/>
     </row>
     <row r="33" spans="2:9">
       <c r="B33" s="66" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" s="119" t="s">
         <v>211</v>
-      </c>
-      <c r="F33" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="119" t="s">
-        <v>212</v>
       </c>
       <c r="I33" s="110"/>
     </row>
     <row r="34" spans="2:9">
       <c r="B34" s="66" t="s">
+        <v>212</v>
+      </c>
+      <c r="F34" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="57" t="s">
+      <c r="H34" s="109" t="s">
         <v>214</v>
-      </c>
-      <c r="H34" s="109" t="s">
-        <v>215</v>
       </c>
       <c r="I34" s="69"/>
     </row>
     <row r="35" spans="2:9">
       <c r="B35" s="66" t="s">
+        <v>215</v>
+      </c>
+      <c r="F35" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="F35" s="59" t="s">
+      <c r="H35" s="114" t="s">
         <v>217</v>
-      </c>
-      <c r="H35" s="114" t="s">
-        <v>218</v>
       </c>
       <c r="I35" s="109"/>
     </row>
     <row r="36" spans="2:9">
       <c r="B36" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="F36" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="F36" s="57" t="s">
+      <c r="H36" s="111" t="s">
         <v>220</v>
-      </c>
-      <c r="H36" s="111" t="s">
-        <v>221</v>
       </c>
       <c r="I36" s="102"/>
     </row>
     <row r="37" spans="2:9">
       <c r="B37" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="F37" s="57" t="s">
+      <c r="H37" s="112" t="s">
         <v>223</v>
-      </c>
-      <c r="H37" s="112" t="s">
-        <v>224</v>
       </c>
       <c r="I37" s="110"/>
     </row>
     <row r="38" spans="2:9">
       <c r="B38" s="66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F38" s="57" t="s">
         <v>26</v>
       </c>
       <c r="H38" s="109" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I38" s="109"/>
     </row>
     <row r="39" spans="2:9" ht="27.6">
       <c r="B39" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="F39" s="57" t="s">
         <v>227</v>
       </c>
-      <c r="F39" s="57" t="s">
+      <c r="H39" s="109" t="s">
         <v>228</v>
-      </c>
-      <c r="H39" s="109" t="s">
-        <v>229</v>
       </c>
       <c r="I39" s="111"/>
     </row>
     <row r="40" spans="2:9">
       <c r="B40" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="59" t="s">
         <v>230</v>
       </c>
-      <c r="F40" s="59" t="s">
+      <c r="H40" s="69" t="s">
         <v>231</v>
-      </c>
-      <c r="H40" s="69" t="s">
-        <v>232</v>
       </c>
       <c r="I40" s="112"/>
     </row>
     <row r="41" spans="2:9">
       <c r="B41" s="66" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D41" s="63"/>
       <c r="H41" s="111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I41" s="112"/>
     </row>
     <row r="42" spans="2:9">
       <c r="B42" s="66" t="s">
+        <v>234</v>
+      </c>
+      <c r="H42" s="112" t="s">
         <v>235</v>
-      </c>
-      <c r="H42" s="112" t="s">
-        <v>236</v>
       </c>
       <c r="I42" s="109"/>
     </row>
     <row r="43" spans="2:9">
       <c r="B43" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="H43" s="109" t="s">
         <v>237</v>
-      </c>
-      <c r="H43" s="109" t="s">
-        <v>238</v>
       </c>
       <c r="I43" s="111"/>
     </row>
     <row r="44" spans="2:9">
       <c r="B44" s="121" t="s">
+        <v>238</v>
+      </c>
+      <c r="H44" s="111" t="s">
         <v>239</v>
-      </c>
-      <c r="H44" s="111" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="45" spans="2:9">
       <c r="H45" s="112" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I45" s="110"/>
     </row>
     <row r="46" spans="2:9">
       <c r="H46" s="70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I46" s="113"/>
     </row>
     <row r="47" spans="2:9">
       <c r="B47" s="62"/>
       <c r="H47" s="112" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I47" s="112"/>
     </row>
     <row r="48" spans="2:9">
       <c r="H48" s="70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I48" s="112"/>
     </row>
     <row r="49" spans="8:9">
       <c r="H49" s="109" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I49" s="112"/>
     </row>
     <row r="50" spans="8:9">
       <c r="H50" s="70" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I50" s="112"/>
     </row>
     <row r="51" spans="8:9">
       <c r="H51" s="69" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I51" s="112"/>
     </row>
     <row r="52" spans="8:9">
       <c r="H52" s="112" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="8:9">
       <c r="H53" s="109" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I53" s="112"/>
     </row>
     <row r="54" spans="8:9">
       <c r="H54" s="69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I54" s="111"/>
     </row>
     <row r="55" spans="8:9">
       <c r="H55" s="70" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I55" s="111"/>
     </row>
     <row r="56" spans="8:9">
       <c r="H56" s="109" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I56" s="70"/>
     </row>
     <row r="57" spans="8:9">
       <c r="H57" s="70" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I57" s="112"/>
     </row>
     <row r="58" spans="8:9">
       <c r="H58" s="70" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I58" s="112"/>
     </row>
     <row r="59" spans="8:9">
       <c r="H59" s="112" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I59" s="115"/>
     </row>
     <row r="60" spans="8:9">
       <c r="H60" s="115" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I60" s="69"/>
     </row>
     <row r="61" spans="8:9">
       <c r="H61" s="69" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I61" s="110"/>
     </row>
     <row r="62" spans="8:9">
       <c r="H62" s="69" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I62" s="69"/>
     </row>
     <row r="63" spans="8:9">
       <c r="H63" s="110" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="64" spans="8:9">
       <c r="H64" s="120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="65" spans="8:8">
@@ -13369,6 +13366,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -13506,23 +13518,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13530,7 +13527,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA7CA51-3876-42E5-9D60-4320955E597F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84037CEB-E5D3-4F40-B93D-B68754BA7EB6}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
